--- a/docentes/Medina Tolentino Francisco - Estadisticos 20211.xlsx
+++ b/docentes/Medina Tolentino Francisco - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="74">
   <si>
     <t>Mat</t>
   </si>
@@ -73,16 +73,49 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
     <t>VEGA</t>
   </si>
   <si>
+    <t>ZETINA</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>ARELLANO</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>ALVARADO</t>
+  </si>
+  <si>
+    <t>CIRUELO</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
-    <t>MIXCOHUA</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
+    <t>CHACÓN</t>
+  </si>
+  <si>
+    <t>CERON</t>
   </si>
   <si>
     <t>ROMERO</t>
@@ -91,142 +124,115 @@
     <t>DE LOS SANTOS</t>
   </si>
   <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>ALVARADO</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>ROMANOS</t>
-  </si>
-  <si>
-    <t>CHACÓN</t>
+    <t>TENTZOHUA</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>DEL ROSARIO</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>VALLEJO</t>
+  </si>
+  <si>
+    <t>BRAVO</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>NAJERA</t>
   </si>
   <si>
     <t>JIMENEZ</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>TENTZOHUA</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
+    <t>LEPE</t>
   </si>
   <si>
     <t>YOPIHUA</t>
   </si>
   <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
   </si>
   <si>
     <t>QUIÑONES</t>
   </si>
   <si>
-    <t>MACARIO</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>CASTELLANOS</t>
-  </si>
-  <si>
-    <t>LEPE</t>
-  </si>
-  <si>
-    <t>TEZOCO</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
     <t>LEÓN</t>
   </si>
   <si>
     <t>LINARES</t>
   </si>
   <si>
+    <t>CARLA ESTEFANIA</t>
+  </si>
+  <si>
     <t>HANIA ZARETH</t>
   </si>
   <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>INGRID AMERICA</t>
+  </si>
+  <si>
+    <t>JAIME</t>
+  </si>
+  <si>
+    <t>LUIS REY</t>
+  </si>
+  <si>
+    <t>PEDRO ANGEL</t>
+  </si>
+  <si>
+    <t>DAVID OSWALDO</t>
+  </si>
+  <si>
+    <t>ALBERTO SHAKIB</t>
+  </si>
+  <si>
+    <t>PATRICIA</t>
+  </si>
+  <si>
+    <t>GABRIELA ELIZABETH</t>
+  </si>
+  <si>
+    <t>MICHEL</t>
+  </si>
+  <si>
+    <t>ANGEL GABRIEL</t>
+  </si>
+  <si>
     <t>PAOLA JAZMIN</t>
   </si>
   <si>
-    <t>ANGELINA</t>
-  </si>
-  <si>
-    <t>LUIS REY</t>
+    <t>KATHIA</t>
+  </si>
+  <si>
+    <t>FERGIE PAULETTE</t>
+  </si>
+  <si>
+    <t>FATIMA</t>
   </si>
   <si>
     <t>CITLALI ESPERANZA</t>
   </si>
   <si>
     <t>GABRIELA</t>
-  </si>
-  <si>
-    <t>FLOR GUADALUPE</t>
-  </si>
-  <si>
-    <t>PEDRO ANGEL</t>
-  </si>
-  <si>
-    <t>DAVID OSWALDO</t>
-  </si>
-  <si>
-    <t>PATRICIA</t>
-  </si>
-  <si>
-    <t>MICHEL</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
-  </si>
-  <si>
-    <t>ANGEL GABRIEL</t>
-  </si>
-  <si>
-    <t>DANIELA</t>
-  </si>
-  <si>
-    <t>KATHIA</t>
-  </si>
-  <si>
-    <t>REGINA ISABEL</t>
-  </si>
-  <si>
-    <t>VANESSA</t>
   </si>
   <si>
     <t>RUBI</t>
@@ -633,19 +639,19 @@
         <v>44</v>
       </c>
       <c r="D2">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G2">
-        <v>50</v>
+        <v>54.55</v>
       </c>
       <c r="H2">
-        <v>8.800000000000001</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -659,19 +665,19 @@
         <v>43</v>
       </c>
       <c r="D3">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G3">
-        <v>53.49</v>
+        <v>58.14</v>
       </c>
       <c r="H3">
-        <v>8.4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -685,10 +691,10 @@
         <v>21</v>
       </c>
       <c r="D4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4">
         <v>11</v>
@@ -697,7 +703,7 @@
         <v>52.38</v>
       </c>
       <c r="H4">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -750,16 +756,19 @@
         <v>44</v>
       </c>
       <c r="D2">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="E2">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>34.09</v>
+      </c>
+      <c r="H2">
+        <v>8.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -773,16 +782,19 @@
         <v>43</v>
       </c>
       <c r="D3">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="E3">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>37.21</v>
+      </c>
+      <c r="H3">
+        <v>8.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -796,16 +808,19 @@
         <v>21</v>
       </c>
       <c r="D4">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="E4">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>47.62</v>
+      </c>
+      <c r="H4">
+        <v>8.5</v>
       </c>
     </row>
   </sheetData>
@@ -858,19 +873,19 @@
         <v>44</v>
       </c>
       <c r="D2">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G2">
-        <v>50</v>
+        <v>59.09</v>
       </c>
       <c r="H2">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -884,16 +899,16 @@
         <v>43</v>
       </c>
       <c r="D3">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G3">
-        <v>53.49</v>
+        <v>62.79</v>
       </c>
       <c r="H3">
         <v>8.4</v>
@@ -910,19 +925,19 @@
         <v>21</v>
       </c>
       <c r="D4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G4">
-        <v>52.38</v>
+        <v>57.14</v>
       </c>
       <c r="H4">
-        <v>8.5</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -932,7 +947,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -964,7 +979,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920067</v>
+        <v>21330051920037</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
@@ -982,12 +997,12 @@
         <v>9</v>
       </c>
       <c r="G2">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920185</v>
+        <v>21330051920067</v>
       </c>
       <c r="B3" t="s">
         <v>19</v>
@@ -1005,12 +1020,12 @@
         <v>9</v>
       </c>
       <c r="G3">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920088</v>
+        <v>21330051920070</v>
       </c>
       <c r="B4" t="s">
         <v>20</v>
@@ -1025,15 +1040,15 @@
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G4">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920099</v>
+        <v>21330051920094</v>
       </c>
       <c r="B5" t="s">
         <v>21</v>
@@ -1051,18 +1066,18 @@
         <v>10</v>
       </c>
       <c r="G5">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920101</v>
+        <v>21330051920096</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="D6" t="s">
         <v>57</v>
@@ -1074,18 +1089,18 @@
         <v>10</v>
       </c>
       <c r="G6">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920104</v>
+        <v>21330051920099</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="D7" t="s">
         <v>58</v>
@@ -1097,15 +1112,15 @@
         <v>10</v>
       </c>
       <c r="G7">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920387</v>
+        <v>21330051920135</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C8" t="s">
         <v>42</v>
@@ -1117,18 +1132,18 @@
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G8">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920135</v>
+        <v>21330051920136</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C9" t="s">
         <v>43</v>
@@ -1143,15 +1158,15 @@
         <v>11</v>
       </c>
       <c r="G9">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920136</v>
+        <v>21330051920141</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C10" t="s">
         <v>44</v>
@@ -1166,7 +1181,7 @@
         <v>11</v>
       </c>
       <c r="G10">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -1174,7 +1189,7 @@
         <v>21330051920030</v>
       </c>
       <c r="B11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C11" t="s">
         <v>28</v>
@@ -1189,18 +1204,18 @@
         <v>9</v>
       </c>
       <c r="G11">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920048</v>
+        <v>21330051920035</v>
       </c>
       <c r="B12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C12" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="D12" t="s">
         <v>63</v>
@@ -1212,15 +1227,15 @@
         <v>9</v>
       </c>
       <c r="G12">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920051</v>
+        <v>21330051920048</v>
       </c>
       <c r="B13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C13" t="s">
         <v>45</v>
@@ -1235,7 +1250,7 @@
         <v>9</v>
       </c>
       <c r="G13">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -1243,7 +1258,7 @@
         <v>21330051920054</v>
       </c>
       <c r="B14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C14" t="s">
         <v>46</v>
@@ -1258,15 +1273,15 @@
         <v>9</v>
       </c>
       <c r="G14">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920059</v>
+        <v>20330051920185</v>
       </c>
       <c r="B15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C15" t="s">
         <v>47</v>
@@ -1281,7 +1296,7 @@
         <v>9</v>
       </c>
       <c r="G15">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -1289,7 +1304,7 @@
         <v>21330051920072</v>
       </c>
       <c r="B16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C16" t="s">
         <v>48</v>
@@ -1304,15 +1319,15 @@
         <v>10</v>
       </c>
       <c r="G16">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920083</v>
+        <v>21330051920073</v>
       </c>
       <c r="B17" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C17" t="s">
         <v>49</v>
@@ -1327,18 +1342,18 @@
         <v>10</v>
       </c>
       <c r="G17">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>21330051920084</v>
+        <v>21330051920086</v>
       </c>
       <c r="B18" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C18" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D18" t="s">
         <v>69</v>
@@ -1350,18 +1365,18 @@
         <v>10</v>
       </c>
       <c r="G18">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>21330051920107</v>
+        <v>21330051920101</v>
       </c>
       <c r="B19" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C19" t="s">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="D19" t="s">
         <v>70</v>
@@ -1373,18 +1388,18 @@
         <v>10</v>
       </c>
       <c r="G19">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>21330051920108</v>
+        <v>21330051920104</v>
       </c>
       <c r="B20" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C20" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D20" t="s">
         <v>71</v>
@@ -1396,7 +1411,53 @@
         <v>10</v>
       </c>
       <c r="G20">
-        <v>6</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>21330051920107</v>
+      </c>
+      <c r="B21" t="s">
+        <v>35</v>
+      </c>
+      <c r="C21" t="s">
+        <v>51</v>
+      </c>
+      <c r="D21" t="s">
+        <v>72</v>
+      </c>
+      <c r="E21" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" t="s">
+        <v>10</v>
+      </c>
+      <c r="G21">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>21330051920108</v>
+      </c>
+      <c r="B22" t="s">
+        <v>36</v>
+      </c>
+      <c r="C22" t="s">
+        <v>52</v>
+      </c>
+      <c r="D22" t="s">
+        <v>73</v>
+      </c>
+      <c r="E22" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" t="s">
+        <v>10</v>
+      </c>
+      <c r="G22">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Medina Tolentino Francisco - Estadisticos 20211.xlsx
+++ b/docentes/Medina Tolentino Francisco - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="79">
   <si>
     <t>Mat</t>
   </si>
@@ -76,6 +76,9 @@
     <t>DE LA CRUZ</t>
   </si>
   <si>
+    <t>FLORES</t>
+  </si>
+  <si>
     <t>VEGA</t>
   </si>
   <si>
@@ -97,6 +100,9 @@
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>SALAZAR</t>
+  </si>
+  <si>
     <t>ALVARADO</t>
   </si>
   <si>
@@ -133,6 +139,9 @@
     <t>DEL ROSARIO</t>
   </si>
   <si>
+    <t>CELESTINO</t>
+  </si>
+  <si>
     <t>ROJAS</t>
   </si>
   <si>
@@ -181,6 +190,9 @@
     <t>CARLA ESTEFANIA</t>
   </si>
   <si>
+    <t>KARLA JIMENA</t>
+  </si>
+  <si>
     <t>HANIA ZARETH</t>
   </si>
   <si>
@@ -203,6 +215,9 @@
   </si>
   <si>
     <t>ALBERTO SHAKIB</t>
+  </si>
+  <si>
+    <t>LUIS GUILLERMO</t>
   </si>
   <si>
     <t>PATRICIA</t>
@@ -947,7 +962,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -985,10 +1000,10 @@
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1002,16 +1017,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920067</v>
+        <v>21330051920390</v>
       </c>
       <c r="B3" t="s">
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D3" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1020,21 +1035,21 @@
         <v>9</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920070</v>
+        <v>21330051920067</v>
       </c>
       <c r="B4" t="s">
         <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1048,39 +1063,39 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920094</v>
+        <v>21330051920070</v>
       </c>
       <c r="B5" t="s">
         <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G5">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920096</v>
+        <v>21330051920094</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D6" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1089,21 +1104,21 @@
         <v>10</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920099</v>
+        <v>21330051920096</v>
       </c>
       <c r="B7" t="s">
         <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="D7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1117,39 +1132,39 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920135</v>
+        <v>21330051920099</v>
       </c>
       <c r="B8" t="s">
         <v>23</v>
       </c>
       <c r="C8" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="D8" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G8">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920136</v>
+        <v>21330051920135</v>
       </c>
       <c r="B9" t="s">
         <v>24</v>
       </c>
       <c r="C9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D9" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1158,21 +1173,21 @@
         <v>11</v>
       </c>
       <c r="G9">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920141</v>
+        <v>21330051920136</v>
       </c>
       <c r="B10" t="s">
         <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D10" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1181,67 +1196,67 @@
         <v>11</v>
       </c>
       <c r="G10">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920030</v>
+        <v>21330051920141</v>
       </c>
       <c r="B11" t="s">
         <v>26</v>
       </c>
       <c r="C11" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="D11" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920035</v>
+        <v>21330051920382</v>
       </c>
       <c r="B12" t="s">
         <v>27</v>
       </c>
       <c r="C12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D12" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G12">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920048</v>
+        <v>21330051920030</v>
       </c>
       <c r="B13" t="s">
         <v>28</v>
       </c>
       <c r="C13" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="D13" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1255,16 +1270,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920054</v>
+        <v>21330051920035</v>
       </c>
       <c r="B14" t="s">
         <v>29</v>
       </c>
       <c r="C14" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="D14" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1273,21 +1288,21 @@
         <v>9</v>
       </c>
       <c r="G14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920185</v>
+        <v>21330051920048</v>
       </c>
       <c r="B15" t="s">
         <v>30</v>
       </c>
       <c r="C15" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D15" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1296,50 +1311,50 @@
         <v>9</v>
       </c>
       <c r="G15">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920072</v>
+        <v>21330051920054</v>
       </c>
       <c r="B16" t="s">
         <v>31</v>
       </c>
       <c r="C16" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D16" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G16">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920073</v>
+        <v>20330051920185</v>
       </c>
       <c r="B17" t="s">
         <v>32</v>
       </c>
       <c r="C17" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D17" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -1347,16 +1362,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>21330051920086</v>
+        <v>21330051920072</v>
       </c>
       <c r="B18" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C18" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="D18" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1365,21 +1380,21 @@
         <v>10</v>
       </c>
       <c r="G18">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>21330051920101</v>
+        <v>21330051920073</v>
       </c>
       <c r="B19" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C19" t="s">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="D19" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -1388,21 +1403,21 @@
         <v>10</v>
       </c>
       <c r="G19">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>21330051920104</v>
+        <v>21330051920086</v>
       </c>
       <c r="B20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C20" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D20" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -1411,21 +1426,21 @@
         <v>10</v>
       </c>
       <c r="G20">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>21330051920107</v>
+        <v>21330051920101</v>
       </c>
       <c r="B21" t="s">
         <v>35</v>
       </c>
       <c r="C21" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="D21" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -1434,21 +1449,21 @@
         <v>10</v>
       </c>
       <c r="G21">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>21330051920108</v>
+        <v>21330051920104</v>
       </c>
       <c r="B22" t="s">
         <v>36</v>
       </c>
       <c r="C22" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D22" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -1457,6 +1472,52 @@
         <v>10</v>
       </c>
       <c r="G22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>21330051920107</v>
+      </c>
+      <c r="B23" t="s">
+        <v>37</v>
+      </c>
+      <c r="C23" t="s">
+        <v>54</v>
+      </c>
+      <c r="D23" t="s">
+        <v>77</v>
+      </c>
+      <c r="E23" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" t="s">
+        <v>10</v>
+      </c>
+      <c r="G23">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>21330051920108</v>
+      </c>
+      <c r="B24" t="s">
+        <v>38</v>
+      </c>
+      <c r="C24" t="s">
+        <v>55</v>
+      </c>
+      <c r="D24" t="s">
+        <v>78</v>
+      </c>
+      <c r="E24" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" t="s">
+        <v>10</v>
+      </c>
+      <c r="G24">
         <v>2</v>
       </c>
     </row>

--- a/docentes/Medina Tolentino Francisco - Estadisticos 20211.xlsx
+++ b/docentes/Medina Tolentino Francisco - Estadisticos 20211.xlsx
@@ -706,19 +706,19 @@
         <v>21</v>
       </c>
       <c r="D4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="F4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G4">
-        <v>52.38</v>
+        <v>57.14</v>
       </c>
       <c r="H4">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
     </row>
   </sheetData>
@@ -826,7 +826,7 @@
         <v>11</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4">
         <v>10</v>
@@ -940,19 +940,19 @@
         <v>21</v>
       </c>
       <c r="D4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G4">
-        <v>57.14</v>
+        <v>61.9</v>
       </c>
       <c r="H4">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Medina Tolentino Francisco - Estadisticos 20211.xlsx
+++ b/docentes/Medina Tolentino Francisco - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="77">
   <si>
     <t>Mat</t>
   </si>
@@ -109,21 +109,21 @@
     <t>CIRUELO</t>
   </si>
   <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>CHACÓN</t>
+  </si>
+  <si>
+    <t>CERON</t>
+  </si>
+  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>CHACÓN</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
     <t>ROMERO</t>
   </si>
   <si>
@@ -163,9 +163,6 @@
     <t>NAJERA</t>
   </si>
   <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
     <t>LEPE</t>
   </si>
   <si>
@@ -224,9 +221,6 @@
   </si>
   <si>
     <t>GABRIELA ELIZABETH</t>
-  </si>
-  <si>
-    <t>MICHEL</t>
   </si>
   <si>
     <t>ANGEL GABRIEL</t>
@@ -654,16 +648,16 @@
         <v>44</v>
       </c>
       <c r="D2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E2">
         <v>2</v>
       </c>
       <c r="F2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G2">
-        <v>54.55</v>
+        <v>56.82</v>
       </c>
       <c r="H2">
         <v>8.300000000000001</v>
@@ -771,19 +765,19 @@
         <v>44</v>
       </c>
       <c r="D2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E2">
         <v>11</v>
       </c>
       <c r="F2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G2">
-        <v>34.09</v>
+        <v>36.36</v>
       </c>
       <c r="H2">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -797,19 +791,19 @@
         <v>43</v>
       </c>
       <c r="D3">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E3">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G3">
-        <v>37.21</v>
+        <v>44.19</v>
       </c>
       <c r="H3">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -823,19 +817,19 @@
         <v>21</v>
       </c>
       <c r="D4">
+        <v>10</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4">
         <v>11</v>
       </c>
-      <c r="E4">
-        <v>3</v>
-      </c>
-      <c r="F4">
-        <v>10</v>
-      </c>
       <c r="G4">
-        <v>47.62</v>
+        <v>52.38</v>
       </c>
       <c r="H4">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
     </row>
   </sheetData>
@@ -888,19 +882,19 @@
         <v>44</v>
       </c>
       <c r="D2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G2">
-        <v>59.09</v>
+        <v>61.36</v>
       </c>
       <c r="H2">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -926,7 +920,7 @@
         <v>62.79</v>
       </c>
       <c r="H3">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -952,7 +946,7 @@
         <v>61.9</v>
       </c>
       <c r="H4">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -962,7 +956,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1003,7 +997,7 @@
         <v>39</v>
       </c>
       <c r="D2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1026,7 +1020,7 @@
         <v>40</v>
       </c>
       <c r="D3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1049,7 +1043,7 @@
         <v>41</v>
       </c>
       <c r="D4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1072,7 +1066,7 @@
         <v>42</v>
       </c>
       <c r="D5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1095,7 +1089,7 @@
         <v>43</v>
       </c>
       <c r="D6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1118,7 +1112,7 @@
         <v>44</v>
       </c>
       <c r="D7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1141,7 +1135,7 @@
         <v>22</v>
       </c>
       <c r="D8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1164,7 +1158,7 @@
         <v>45</v>
       </c>
       <c r="D9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1187,7 +1181,7 @@
         <v>46</v>
       </c>
       <c r="D10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1210,7 +1204,7 @@
         <v>47</v>
       </c>
       <c r="D11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1233,7 +1227,7 @@
         <v>26</v>
       </c>
       <c r="D12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1253,10 +1247,10 @@
         <v>28</v>
       </c>
       <c r="C13" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1279,7 +1273,7 @@
         <v>26</v>
       </c>
       <c r="D14" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1293,7 +1287,7 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920048</v>
+        <v>21330051920054</v>
       </c>
       <c r="B15" t="s">
         <v>30</v>
@@ -1302,7 +1296,7 @@
         <v>48</v>
       </c>
       <c r="D15" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1311,12 +1305,12 @@
         <v>9</v>
       </c>
       <c r="G15">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920054</v>
+        <v>20330051920185</v>
       </c>
       <c r="B16" t="s">
         <v>31</v>
@@ -1325,7 +1319,7 @@
         <v>49</v>
       </c>
       <c r="D16" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1334,12 +1328,12 @@
         <v>9</v>
       </c>
       <c r="G16">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>20330051920185</v>
+        <v>21330051920072</v>
       </c>
       <c r="B17" t="s">
         <v>32</v>
@@ -1348,13 +1342,13 @@
         <v>50</v>
       </c>
       <c r="D17" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -1362,7 +1356,7 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>21330051920072</v>
+        <v>21330051920073</v>
       </c>
       <c r="B18" t="s">
         <v>33</v>
@@ -1371,7 +1365,7 @@
         <v>51</v>
       </c>
       <c r="D18" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1385,16 +1379,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>21330051920073</v>
+        <v>21330051920086</v>
       </c>
       <c r="B19" t="s">
         <v>34</v>
       </c>
       <c r="C19" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="D19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -1403,21 +1397,21 @@
         <v>10</v>
       </c>
       <c r="G19">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>21330051920086</v>
+        <v>21330051920101</v>
       </c>
       <c r="B20" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C20" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="D20" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -1426,21 +1420,21 @@
         <v>10</v>
       </c>
       <c r="G20">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>21330051920101</v>
+        <v>21330051920104</v>
       </c>
       <c r="B21" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C21" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="D21" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -1449,21 +1443,21 @@
         <v>10</v>
       </c>
       <c r="G21">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>21330051920104</v>
+        <v>21330051920107</v>
       </c>
       <c r="B22" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C22" t="s">
         <v>53</v>
       </c>
       <c r="D22" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -1472,21 +1466,21 @@
         <v>10</v>
       </c>
       <c r="G22">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>21330051920107</v>
+        <v>21330051920108</v>
       </c>
       <c r="B23" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C23" t="s">
         <v>54</v>
       </c>
       <c r="D23" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
@@ -1495,29 +1489,6 @@
         <v>10</v>
       </c>
       <c r="G23">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>21330051920108</v>
-      </c>
-      <c r="B24" t="s">
-        <v>38</v>
-      </c>
-      <c r="C24" t="s">
-        <v>55</v>
-      </c>
-      <c r="D24" t="s">
-        <v>78</v>
-      </c>
-      <c r="E24" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" t="s">
-        <v>10</v>
-      </c>
-      <c r="G24">
         <v>2</v>
       </c>
     </row>

--- a/docentes/Medina Tolentino Francisco - Estadisticos 20211.xlsx
+++ b/docentes/Medina Tolentino Francisco - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="92">
   <si>
     <t>Mat</t>
   </si>
@@ -73,22 +73,73 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>ARAGON</t>
+  </si>
+  <si>
+    <t>COMIHUA</t>
+  </si>
+  <si>
+    <t>CABALLERO</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>PELLICO</t>
+  </si>
+  <si>
+    <t>TENTZOHUA</t>
+  </si>
+  <si>
+    <t>ELPIDIO</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>ORTEGA</t>
+  </si>
+  <si>
+    <t>PEÑA</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
     <t>DE LA CRUZ</t>
   </si>
   <si>
     <t>FLORES</t>
   </si>
   <si>
-    <t>VEGA</t>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>ROMANOS</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
   </si>
   <si>
     <t>ZETINA</t>
   </si>
   <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MIXCOHUA</t>
+  </si>
+  <si>
+    <t>RUGERIO</t>
+  </si>
+  <si>
+    <t>SANJUAN</t>
   </si>
   <si>
     <t>ALVAREZ</t>
@@ -97,112 +148,139 @@
     <t>ARELLANO</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
     <t>SALAZAR</t>
   </si>
   <si>
-    <t>ALVARADO</t>
-  </si>
-  <si>
-    <t>CIRUELO</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>CHACÓN</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>TENTZOHUA</t>
+    <t>BRUNO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>LEYVA</t>
+  </si>
+  <si>
+    <t>CARRILLO</t>
+  </si>
+  <si>
+    <t>BRAVO</t>
+  </si>
+  <si>
+    <t>TEQUIHUATLE</t>
+  </si>
+  <si>
+    <t>LEÓN</t>
   </si>
   <si>
     <t>VAZQUEZ</t>
   </si>
   <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>RIVADENEYRA</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
     <t>DEL ROSARIO</t>
   </si>
   <si>
-    <t>CELESTINO</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
+    <t>ESTRADA</t>
+  </si>
+  <si>
+    <t>TEZOCO</t>
+  </si>
+  <si>
+    <t>GALEOTE</t>
+  </si>
+  <si>
+    <t>YOPIHUA</t>
   </si>
   <si>
     <t>VALLEJO</t>
   </si>
   <si>
-    <t>BRAVO</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
     <t>RIVERA</t>
   </si>
   <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
     <t>JUAREZ</t>
   </si>
   <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>LEPE</t>
-  </si>
-  <si>
-    <t>YOPIHUA</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>QUIÑONES</t>
-  </si>
-  <si>
-    <t>LEÓN</t>
-  </si>
-  <si>
-    <t>LINARES</t>
+    <t>JONATHAN YOSEF</t>
+  </si>
+  <si>
+    <t>ALEJANDRO GABRIEL</t>
+  </si>
+  <si>
+    <t>LUIS ARMANDO</t>
+  </si>
+  <si>
+    <t>JAZMIN ADALI</t>
+  </si>
+  <si>
+    <t>INGRID AMERICA</t>
+  </si>
+  <si>
+    <t>JAZMIN</t>
+  </si>
+  <si>
+    <t>RUBI</t>
+  </si>
+  <si>
+    <t>MARYFER</t>
+  </si>
+  <si>
+    <t>KARLA</t>
+  </si>
+  <si>
+    <t>JOSIAH</t>
+  </si>
+  <si>
+    <t>OLIVER ULISES</t>
+  </si>
+  <si>
+    <t>RONALDO</t>
   </si>
   <si>
     <t>CARLA ESTEFANIA</t>
   </si>
   <si>
-    <t>KARLA JIMENA</t>
-  </si>
-  <si>
-    <t>HANIA ZARETH</t>
+    <t>LAURA FERNANDA</t>
+  </si>
+  <si>
+    <t>DAIRA</t>
+  </si>
+  <si>
+    <t>DANIELA</t>
+  </si>
+  <si>
+    <t>XIMENA</t>
+  </si>
+  <si>
+    <t>PAOLA JAZMIN</t>
   </si>
   <si>
     <t>MARIA FERNANDA</t>
   </si>
   <si>
-    <t>INGRID AMERICA</t>
-  </si>
-  <si>
-    <t>JAIME</t>
-  </si>
-  <si>
-    <t>LUIS REY</t>
+    <t>FATIMA</t>
+  </si>
+  <si>
+    <t>ANGELINA</t>
+  </si>
+  <si>
+    <t>ALDO GEOVANNI</t>
+  </si>
+  <si>
+    <t>KIMBERLY</t>
+  </si>
+  <si>
+    <t>ALMA KAREN</t>
   </si>
   <si>
     <t>PEDRO ANGEL</t>
@@ -215,39 +293,6 @@
   </si>
   <si>
     <t>LUIS GUILLERMO</t>
-  </si>
-  <si>
-    <t>PATRICIA</t>
-  </si>
-  <si>
-    <t>GABRIELA ELIZABETH</t>
-  </si>
-  <si>
-    <t>ANGEL GABRIEL</t>
-  </si>
-  <si>
-    <t>PAOLA JAZMIN</t>
-  </si>
-  <si>
-    <t>KATHIA</t>
-  </si>
-  <si>
-    <t>FERGIE PAULETTE</t>
-  </si>
-  <si>
-    <t>FATIMA</t>
-  </si>
-  <si>
-    <t>CITLALI ESPERANZA</t>
-  </si>
-  <si>
-    <t>GABRIELA</t>
-  </si>
-  <si>
-    <t>RUBI</t>
-  </si>
-  <si>
-    <t>MARYFER</t>
   </si>
 </sst>
 </file>
@@ -648,19 +693,19 @@
         <v>44</v>
       </c>
       <c r="D2">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F2">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="G2">
-        <v>56.82</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="H2">
-        <v>8.300000000000001</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -674,19 +719,19 @@
         <v>43</v>
       </c>
       <c r="D3">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="F3">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="G3">
-        <v>58.14</v>
+        <v>69.77</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -700,10 +745,10 @@
         <v>21</v>
       </c>
       <c r="D4">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F4">
         <v>12</v>
@@ -712,7 +757,7 @@
         <v>57.14</v>
       </c>
       <c r="H4">
-        <v>8.1</v>
+        <v>6.9</v>
       </c>
     </row>
   </sheetData>
@@ -765,19 +810,19 @@
         <v>44</v>
       </c>
       <c r="D2">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="G2">
-        <v>36.36</v>
+        <v>86.36</v>
       </c>
       <c r="H2">
-        <v>7.9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -791,19 +836,19 @@
         <v>43</v>
       </c>
       <c r="D3">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F3">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="G3">
-        <v>44.19</v>
+        <v>76.73999999999999</v>
       </c>
       <c r="H3">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -817,19 +862,19 @@
         <v>21</v>
       </c>
       <c r="D4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F4">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G4">
-        <v>52.38</v>
+        <v>61.9</v>
       </c>
       <c r="H4">
-        <v>8.4</v>
+        <v>6.9</v>
       </c>
     </row>
   </sheetData>
@@ -882,19 +927,19 @@
         <v>44</v>
       </c>
       <c r="D2">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F2">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="G2">
-        <v>61.36</v>
+        <v>79.55</v>
       </c>
       <c r="H2">
-        <v>8.6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -908,19 +953,19 @@
         <v>43</v>
       </c>
       <c r="D3">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F3">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G3">
-        <v>62.79</v>
+        <v>69.77</v>
       </c>
       <c r="H3">
-        <v>8.5</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -934,10 +979,10 @@
         <v>21</v>
       </c>
       <c r="D4">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F4">
         <v>13</v>
@@ -946,7 +991,7 @@
         <v>61.9</v>
       </c>
       <c r="H4">
-        <v>8.800000000000001</v>
+        <v>7.2</v>
       </c>
     </row>
   </sheetData>
@@ -956,7 +1001,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -988,16 +1033,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920037</v>
+        <v>21330051920388</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D2" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1011,16 +1056,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920390</v>
+        <v>21330051920036</v>
       </c>
       <c r="B3" t="s">
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D3" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1034,22 +1079,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920067</v>
+        <v>21330051920357</v>
       </c>
       <c r="B4" t="s">
         <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D4" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1057,22 +1102,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920070</v>
+        <v>21330051920389</v>
       </c>
       <c r="B5" t="s">
         <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D5" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1086,10 +1131,10 @@
         <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D6" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1098,21 +1143,21 @@
         <v>10</v>
       </c>
       <c r="G6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920096</v>
+        <v>21330051920097</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D7" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1126,16 +1171,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920099</v>
+        <v>21330051920107</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="D8" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1149,39 +1194,39 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920135</v>
+        <v>21330051920108</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="D9" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920136</v>
+        <v>21330051920144</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D10" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1190,21 +1235,21 @@
         <v>11</v>
       </c>
       <c r="G10">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920141</v>
+        <v>21330051920384</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D11" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1213,21 +1258,21 @@
         <v>11</v>
       </c>
       <c r="G11">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920382</v>
+        <v>21330051920395</v>
       </c>
       <c r="B12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C12" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="D12" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1236,27 +1281,27 @@
         <v>11</v>
       </c>
       <c r="G12">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920030</v>
+        <v>21330051920147</v>
       </c>
       <c r="B13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C13" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="D13" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G13">
         <v>2</v>
@@ -1264,16 +1309,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920035</v>
+        <v>21330051920037</v>
       </c>
       <c r="B14" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C14" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="D14" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1287,16 +1332,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920054</v>
+        <v>21330051920039</v>
       </c>
       <c r="B15" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C15" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="D15" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1305,21 +1350,21 @@
         <v>9</v>
       </c>
       <c r="G15">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>20330051920185</v>
+        <v>21330051920052</v>
       </c>
       <c r="B16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C16" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D16" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1333,22 +1378,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920072</v>
+        <v>21330051920059</v>
       </c>
       <c r="B17" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C17" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D17" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -1356,22 +1401,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>21330051920073</v>
+        <v>21330051920065</v>
       </c>
       <c r="B18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C18" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="D18" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -1379,62 +1424,62 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>21330051920086</v>
+        <v>20330051920185</v>
       </c>
       <c r="B19" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C19" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="D19" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G19">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>21330051920101</v>
+        <v>21330051920070</v>
       </c>
       <c r="B20" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C20" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="D20" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G20">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>21330051920104</v>
+        <v>21330051920086</v>
       </c>
       <c r="B21" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C21" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="D21" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -1448,16 +1493,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>21330051920107</v>
+        <v>21330051920088</v>
       </c>
       <c r="B22" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C22" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="D22" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -1466,21 +1511,21 @@
         <v>10</v>
       </c>
       <c r="G22">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>21330051920108</v>
+        <v>21330051920098</v>
       </c>
       <c r="B23" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="C23" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="D23" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
@@ -1489,7 +1534,145 @@
         <v>10</v>
       </c>
       <c r="G23">
-        <v>2</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>21330051920383</v>
+      </c>
+      <c r="B24" t="s">
+        <v>39</v>
+      </c>
+      <c r="C24" t="s">
+        <v>45</v>
+      </c>
+      <c r="D24" t="s">
+        <v>86</v>
+      </c>
+      <c r="E24" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" t="s">
+        <v>10</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>21330051920103</v>
+      </c>
+      <c r="B25" t="s">
+        <v>40</v>
+      </c>
+      <c r="C25" t="s">
+        <v>37</v>
+      </c>
+      <c r="D25" t="s">
+        <v>87</v>
+      </c>
+      <c r="E25" t="s">
+        <v>8</v>
+      </c>
+      <c r="F25" t="s">
+        <v>10</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
+        <v>21330051920135</v>
+      </c>
+      <c r="B26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C26" t="s">
+        <v>61</v>
+      </c>
+      <c r="D26" t="s">
+        <v>88</v>
+      </c>
+      <c r="E26" t="s">
+        <v>8</v>
+      </c>
+      <c r="F26" t="s">
+        <v>11</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27">
+        <v>21330051920136</v>
+      </c>
+      <c r="B27" t="s">
+        <v>42</v>
+      </c>
+      <c r="C27" t="s">
+        <v>63</v>
+      </c>
+      <c r="D27" t="s">
+        <v>89</v>
+      </c>
+      <c r="E27" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" t="s">
+        <v>11</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28">
+        <v>21330051920141</v>
+      </c>
+      <c r="B28" t="s">
+        <v>21</v>
+      </c>
+      <c r="C28" t="s">
+        <v>32</v>
+      </c>
+      <c r="D28" t="s">
+        <v>90</v>
+      </c>
+      <c r="E28" t="s">
+        <v>8</v>
+      </c>
+      <c r="F28" t="s">
+        <v>11</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29">
+        <v>21330051920382</v>
+      </c>
+      <c r="B29" t="s">
+        <v>43</v>
+      </c>
+      <c r="C29" t="s">
+        <v>21</v>
+      </c>
+      <c r="D29" t="s">
+        <v>91</v>
+      </c>
+      <c r="E29" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" t="s">
+        <v>11</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
